--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-390.2%</t>
+          <t>-390.3%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-91.8%</t>
+          <t>-91.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.8%</t>
+          <t>-58.9%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705544</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628915</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575947</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430981</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077638</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.44152978400062</v>
+        <v>3.441529784000616</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.286081842614249</v>
+        <v>-2.287312852111983</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.164498622836592</v>
+        <v>2.164006219037499</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.321927854343416</v>
+        <v>1.320696844845682</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.872444496802089</v>
+        <v>3.871705891103448</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.6%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.9%</t>
+          <t>121.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-566.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-59.7%</t>
+          <t>-62.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.0%</t>
+          <t>646.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-390.3%</t>
+          <t>-417.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-227.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.8%</t>
+          <t>-170.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-91.9%</t>
+          <t>-118.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-185.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-74.9%</t>
         </is>
       </c>
     </row>
@@ -43687,16 +43687,16 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>1.242410788905723</v>
+        <v>0.9733846798089471</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.62667717033905</v>
+        <v>3.51906672670034</v>
       </c>
       <c r="F1832" t="n">
-        <v>2.216275709213999</v>
+        <v>1.947249600117223</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.459834704618908</v>
+        <v>4.298419039160843</v>
       </c>
     </row>
     <row r="1833">
@@ -43704,22 +43704,22 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705544</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>1.194572426659524</v>
+        <v>0.9255463175627483</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.604413879342283</v>
+        <v>3.496803435703573</v>
       </c>
       <c r="F1833" t="n">
-        <v>2.216275709213999</v>
+        <v>1.947249600117223</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.45670675852062</v>
+        <v>4.295291093062554</v>
       </c>
     </row>
     <row r="1834">
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.5896033500544184</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.37540285798363</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.880332741705669</v>
+        <v>1.611306632608893</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.268117587299011</v>
+        <v>4.106701921840946</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.5890515502126062</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.37343997390925</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.612148396094199</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.105464815794474</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.4833646622703066</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.310990491359777</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.597587322391516</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.076553444200312</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.4892140433855509</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.313819382531749</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.597587322391516</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.077042582926186</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4409917765384674</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.298610458414582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.549365055544432</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.052189205439602</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.2038602846886723</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.238698946172206</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.549365055544432</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.087130289937144</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.2088978754162588</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.239291422648579</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.60500951181075</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.119094403882272</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.152428244239962</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.195449951801797</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.063959006800231</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.08666085419054997</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.170160604912502</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.064976615930702</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.07312537041384037</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.155374443389574</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.055604647918457</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.008646530013911302</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.112748409173712</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.575575454040589</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.061908717917378</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.07585563788578897</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.090630082858663</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.575575454040589</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.066674034751079</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.07186418509059878</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.090051460095979</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.57956690683578</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.066893702547434</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.4700126160438594</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.928718979219738</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.181418475882519</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>3.825931535480541</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.6916345496019769</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.839936422395413</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.14389234219515</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.803282071867041</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.8996386079550541</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.761626943608107</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.14389234219515</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.808174216420967</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.170038570663939</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.648548414862542</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>0.8734923794862646</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.641015695133623</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.509196948252461</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.505969363133582</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.5343340018977425</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.430604967886959</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.83721416997994</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.395100764181358</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.2063167801702633</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.25413292458924</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.833877423470969</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.404534213193516</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.2090088125892947</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.263846894449228</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.200588475137515</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.258956184570629</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1577022390772509</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.044926655493033</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.585768866067587</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.103426567011464</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1577022390772509</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.043469194305896</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.92945163929425</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.967722581175415</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.2656082911044691</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>2.980494686544181</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.287101989532598</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.820768499736333</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.6232586413428172</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.76201053505743</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.293762929754746</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.819877050347734</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.6232586413428172</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.76378346175769</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.725568722904534</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.633487620555223</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.7596761377840842</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.668265851360334</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.052001251772277</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.491199384010216</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8421443882912323</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.607069676058135</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.05356540288258</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.48915431522206</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8421443882912323</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.6056502677141</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.417191647782894</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.350191377496176</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.9403660251583581</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.553204845828067</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.414764583254176</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.350416718313495</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.9406988069655098</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.552259691749607</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.823353360434854</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.185742751455983</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.305867969455959</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.236335844575948</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.015735190271006</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.30105340192742</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.652727718862946</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8471724911650842</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.299047452536297</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.02940472939279</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7067603776218254</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.309306143204976</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.043119593717901</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6973739970374759</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.305405708350671</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.355944392962881</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.570648997394485</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.303810628405672</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.360757431428218</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5725027579375586</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.306661623513209</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.794106539538454</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3951368101590607</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.302635318978806</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.177107928281085</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2418341533404242</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.302533217657222</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.552093254452362</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.09441153884334375</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.725819545020251</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.080113537925885</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.911623576956364</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.04405028686020707</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.725819545020251</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.085463841223936</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.238023605621377</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1666942783690346</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-2.052219573685264</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>1.897539843982105</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.231547458827817</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1610620690298421</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.045743426891705</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>1.90446728268001</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.227856533871407</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1595856990472777</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.045743426891705</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>1.90446728268001</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.43211470920127</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2357757720605806</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-2.173382371505693</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>1.833397113030259</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.112060754022666</v>
+        <v>-8.381086863119444</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.103271635504703</v>
+        <v>-0.2108820791434143</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.829146924101817</v>
+        <v>-2.098173033198592</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.044420935957021</v>
+        <v>1.883005270498956</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.038590922355217</v>
+        <v>-8.307617031451995</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.05851200134430234</v>
+        <v>-0.1661224449830137</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.755677092434368</v>
+        <v>-2.024703201531144</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.103874536450911</v>
+        <v>1.942458870992846</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.958218566891287</v>
+        <v>-8.227244675988066</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.01180783841121347</v>
+        <v>-0.1194182820499252</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.675304736970439</v>
+        <v>-1.944330846067214</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.166653170476786</v>
+        <v>2.00523750501872</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.146491369257131</v>
+        <v>-8.415517478353911</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.09433612425914673</v>
+        <v>-0.2019465678978589</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.675304736970439</v>
+        <v>-1.944330846067214</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.15943400557519</v>
+        <v>1.998018340117125</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.166656010806678</v>
+        <v>-8.435682119903458</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.1090741716529418</v>
+        <v>-0.2166846152916539</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.695469378519986</v>
+        <v>-1.964495487616762</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.140663029871485</v>
+        <v>1.97924736441342</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.396480457970503</v>
+        <v>-8.665506567067283</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.1998881606799157</v>
+        <v>-0.3074986043186274</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.858116915590146</v>
+        <v>-2.127143024686922</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.044190297467946</v>
+        <v>1.88277463200988</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.333411225664163</v>
+        <v>-8.602437334760943</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1719667391282651</v>
+        <v>-0.2795771827669769</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.886630478272381</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.02977588848772</v>
+        <v>1.868360223029654</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.28139571169535</v>
+        <v>-8.550421820792129</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.1471701978543387</v>
+        <v>-0.2547806414930509</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.886630478272381</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.03376622417412</v>
+        <v>1.872350558716055</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.362687641249554</v>
+        <v>-8.631713750346334</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1811621965747623</v>
+        <v>-0.288772640213474</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.886630478272381</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.032290997275378</v>
+        <v>1.870875331817313</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.165418235521557</v>
+        <v>-8.434444344618337</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.08720102411869091</v>
+        <v>-0.1948114677574031</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.689361072544382</v>
+        <v>-1.958387181641158</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.16570605087705</v>
+        <v>2.004290385418984</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.966266128284458</v>
+        <v>-8.235292237381238</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.02059131487053456</v>
+        <v>-0.1282017585092463</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524038546594569</v>
+        <v>-1.793064655691345</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.251848432800255</v>
+        <v>2.09043276734219</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.740420975565047</v>
+        <v>-8.009447084661826</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.07932581925343873</v>
+        <v>-0.02828462438527302</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482111871007405</v>
+        <v>-1.751137980104181</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.286583511188762</v>
+        <v>2.125167845730696</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.454146163242353</v>
+        <v>-7.723172272339132</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.1949748887385749</v>
+        <v>0.08736444509986363</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482111871007405</v>
+        <v>-1.751137980104181</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.287722655744821</v>
+        <v>2.126306990286755</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.227350336169019</v>
+        <v>-7.496376445265797</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.2883269937300161</v>
+        <v>0.1807165500913048</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.413997926385861</v>
+        <v>-1.683024035482637</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.331224796679855</v>
+        <v>2.169809131221789</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.94344160524027</v>
+        <v>-7.212467714337048</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4076241903401523</v>
+        <v>0.300013746701441</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.413997926385861</v>
+        <v>-1.683024035482637</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.336958500918491</v>
+        <v>2.175542835460426</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.696454355047318</v>
+        <v>-6.965480464144096</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.4966818280234682</v>
+        <v>0.3890713843847569</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.167010676192909</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.475413588640397</v>
+        <v>2.313997923182332</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.432617487843249</v>
+        <v>-6.701643596940027</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.5923330935921878</v>
+        <v>0.4847226499534769</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.167010676192909</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.46553010732749</v>
+        <v>2.304114441869424</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.165375686974852</v>
+        <v>-6.43440179607163</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.6973952534401731</v>
+        <v>0.5897848098014618</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.167010676192909</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.463695546828116</v>
+        <v>2.302279881370051</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.889566523574368</v>
+        <v>-6.158592632671146</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.807418603826906</v>
+        <v>0.6998081601881947</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.077991367914175</v>
+        <v>-1.347017477010951</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.516806816821895</v>
+        <v>2.35539115136383</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.620498935807388</v>
+        <v>-5.889525044904167</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9157141450791912</v>
+        <v>0.8081037014404799</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.8089237801471961</v>
+        <v>-1.077949889243972</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.678915875627577</v>
+        <v>2.517500210169511</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.356438997484593</v>
+        <v>-5.625465106581371</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.008077804246557</v>
+        <v>0.9004673606078462</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.5448638418244</v>
+        <v>-0.8138899509211759</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.824091522459502</v>
+        <v>2.662675857001437</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.649359373979754</v>
+        <v>-4.918385483076532</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.288122619988192</v>
+        <v>1.180512176349481</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.5448638418244</v>
+        <v>-0.8138899509211759</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.821304488799201</v>
+        <v>2.659888823341136</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.399718343993802</v>
+        <v>-4.66874445309058</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.388322655870414</v>
+        <v>1.280712212231703</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2952228118384482</v>
+        <v>-0.5642489209352242</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.971432730678614</v>
+        <v>2.810017065220548</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.145176444652726</v>
+        <v>-4.414202553749504</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.489506236827602</v>
+        <v>1.38189579318889</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.04068091249737271</v>
+        <v>-0.3097070215941486</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.123524691504016</v>
+        <v>2.96210902604595</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.911695222423128</v>
+        <v>-4.180721331519906</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.590823154557293</v>
+        <v>1.483212710918582</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.1928003097322258</v>
+        <v>-0.0762257993645501</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.271537853679627</v>
+        <v>3.110122188221562</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.731986692279255</v>
+        <v>-4.001012801376033</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.659814356301883</v>
+        <v>1.552203912663172</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.249971813894922</v>
+        <v>-0.01905429520185398</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.302948545864286</v>
+        <v>3.141532880406221</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.599711218648369</v>
+        <v>-3.868737327745147</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.708092032501265</v>
+        <v>1.600481588862553</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.3822472875258086</v>
+        <v>0.1132211784290327</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.377681316789845</v>
+        <v>3.21626565133178</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.409111543975216</v>
+        <v>-3.678137653071994</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.787146963058162</v>
+        <v>1.679536519419451</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.5728469621989615</v>
+        <v>0.3038208531021855</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.494856182281374</v>
+        <v>3.333440516823308</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.160111745291636</v>
+        <v>-3.429137854388414</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.899653223755253</v>
+        <v>1.792042780116542</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.8218467608825422</v>
+        <v>0.5528206517857662</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.65716240271518</v>
+        <v>3.495746737257115</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.968732670430696</v>
+        <v>-3.237758779527474</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.848228924100411</v>
+        <v>1.7406184804617</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.013225835743482</v>
+        <v>0.7441997266467063</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.644013918032526</v>
+        <v>3.48259825257446</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.689705374775069</v>
+        <v>-2.958731483871847</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.008384184239748</v>
+        <v>1.900773740601037</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.013225835743482</v>
+        <v>0.7441997266467063</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.692558259909612</v>
+        <v>3.531142594451547</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.412967200104256</v>
+        <v>-2.681993309201034</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.122458466094067</v>
+        <v>2.014848022455356</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.195042496853408</v>
+        <v>0.9260163877566321</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.805027268561562</v>
+        <v>3.643611603103497</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.441529784000616</v>
+        <v>3.409677455812272</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.287312852111983</v>
+        <v>-2.555100902765965</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.164006219037499</v>
+        <v>2.056890998775906</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.320696844845682</v>
+        <v>1.052908794191702</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.871705891103448</v>
+        <v>3.711033060711061</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.1%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.8%</t>
+          <t>-566.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.2%</t>
+          <t>-62.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>646.1%</t>
+          <t>649.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.1%</t>
+          <t>-417.4%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-227.1%</t>
+          <t>-227.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.5%</t>
+          <t>-170.7%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-308.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-119.1%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-185.3%</t>
+          <t>-185.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-164.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1911"/>
+  <dimension ref="A1:G1912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43681,22 +43681,22 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>0.9733846798089471</v>
+        <v>0.9719539229773715</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.51906672670034</v>
+        <v>3.518494423967709</v>
       </c>
       <c r="F1832" t="n">
-        <v>1.947249600117223</v>
+        <v>1.945818843285647</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.298419039160843</v>
+        <v>4.297560585061897</v>
       </c>
     </row>
     <row r="1833">
@@ -43710,16 +43710,16 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>0.9255463175627483</v>
+        <v>0.9241155607311727</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.496803435703573</v>
+        <v>3.496231132970942</v>
       </c>
       <c r="F1833" t="n">
-        <v>1.947249600117223</v>
+        <v>1.945818843285647</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.295291093062554</v>
+        <v>4.294432638963609</v>
       </c>
     </row>
     <row r="1834">
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.5896033500544184</v>
+        <v>0.588172593222843</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.37540285798363</v>
+        <v>3.374830555251</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.611306632608893</v>
+        <v>1.609875875777317</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.106701921840946</v>
+        <v>4.105843467742001</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5890515502126062</v>
+        <v>0.5876207933810308</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.37343997390925</v>
+        <v>3.372867671176619</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.612148396094199</v>
+        <v>1.610717639262624</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.105464815794474</v>
+        <v>4.104606361695529</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4833646622703066</v>
+        <v>0.4819339054387311</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.310990491359777</v>
+        <v>3.310418188627147</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.597587322391516</v>
+        <v>1.59615656555994</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.076553444200312</v>
+        <v>4.075694990101367</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4892140433855509</v>
+        <v>0.4877832865539755</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.313819382531749</v>
+        <v>3.313247079799119</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.597587322391516</v>
+        <v>1.59615656555994</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.077042582926186</v>
+        <v>4.07618412882724</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4409917765384674</v>
+        <v>0.4395610197068919</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.298610458414582</v>
+        <v>3.298038155681952</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.549365055544432</v>
+        <v>1.547934298712857</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.052189205439602</v>
+        <v>4.051330751340657</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2038602846886723</v>
+        <v>0.2024295278570968</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.238698946172206</v>
+        <v>3.238126643439576</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.549365055544432</v>
+        <v>1.547934298712857</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.087130289937144</v>
+        <v>4.086271835838199</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2088978754162588</v>
+        <v>0.2074671185846834</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.239291422648579</v>
+        <v>3.238719119915948</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.60500951181075</v>
+        <v>1.603578754979174</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.119094403882272</v>
+        <v>4.118235949783327</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.152428244239962</v>
+        <v>0.1509974874083866</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.195449951801797</v>
+        <v>3.194877649069167</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.548539880634453</v>
+        <v>1.547109123802877</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.063959006800231</v>
+        <v>4.063100552701286</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08666085419054997</v>
+        <v>0.08523009735897452</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.170160604912502</v>
+        <v>3.169588302179872</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.548539880634453</v>
+        <v>1.547109123802877</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.064976615930702</v>
+        <v>4.064118161831756</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07312537041384037</v>
+        <v>0.07169461358226492</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.155374443389574</v>
+        <v>3.154802140656944</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.548539880634453</v>
+        <v>1.547109123802877</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.055604647918457</v>
+        <v>4.054746193819511</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.008646530013911302</v>
+        <v>-0.01007728684548675</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.112748409173712</v>
+        <v>3.112176106441082</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.575575454040589</v>
+        <v>1.574144697209014</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.061908717917378</v>
+        <v>4.061050263818432</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07585563788578897</v>
+        <v>-0.07728639471736443</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.090630082858663</v>
+        <v>3.090057780126033</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.575575454040589</v>
+        <v>1.574144697209014</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.066674034751079</v>
+        <v>4.065815580652134</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.07186418509059878</v>
+        <v>-0.07329494192217423</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.090051460095979</v>
+        <v>3.089479157363349</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.57956690683578</v>
+        <v>1.578136150004204</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.066893702547434</v>
+        <v>4.066035248448489</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4700126160438594</v>
+        <v>-0.4714433728754349</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.928718979219738</v>
+        <v>2.928146676487108</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.181418475882519</v>
+        <v>1.179987719050943</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.825931535480541</v>
+        <v>3.825073081381595</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6916345496019769</v>
+        <v>-0.6930653064335524</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.839936422395413</v>
+        <v>2.839364119662783</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.14389234219515</v>
+        <v>1.142461585363574</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.803282071867041</v>
+        <v>3.802423617768096</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8996386079550541</v>
+        <v>-0.9010693647866296</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.761626943608107</v>
+        <v>2.761054640875477</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.14389234219515</v>
+        <v>1.142461585363574</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.808174216420967</v>
+        <v>3.807315762322021</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.170038570663939</v>
+        <v>-1.171469327495515</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.648548414862542</v>
+        <v>2.647976112129911</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8734923794862646</v>
+        <v>0.8720616226546889</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.641015695133623</v>
+        <v>3.640157241034678</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.509196948252461</v>
+        <v>-1.510627705084037</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.505969363133582</v>
+        <v>2.505397060400951</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5343340018977425</v>
+        <v>0.5329032450661668</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.430604967886959</v>
+        <v>3.429746513788014</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.83721416997994</v>
+        <v>-1.838644926811516</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.395100764181358</v>
+        <v>2.394528461448728</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2063167801702633</v>
+        <v>0.2048860233386877</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.25413292458924</v>
+        <v>3.253274470490295</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.833877423470969</v>
+        <v>-1.835308180302545</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.404534213193516</v>
+        <v>2.403961910460885</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2090088125892947</v>
+        <v>0.207578055757719</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.263846894449228</v>
+        <v>3.262988440350282</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.200588475137515</v>
+        <v>-2.20201923196909</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.258956184570629</v>
+        <v>2.258383881837999</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1577022390772509</v>
+        <v>-0.1591329959088266</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.044926655493033</v>
+        <v>3.044068201394087</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.585768866067587</v>
+        <v>-2.587199622899162</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.103426567011464</v>
+        <v>2.102854264278833</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1577022390772509</v>
+        <v>-0.1591329959088266</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.043469194305896</v>
+        <v>3.04261074020695</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.92945163929425</v>
+        <v>-2.930882396125825</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.967722581175415</v>
+        <v>1.967150278442785</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2656082911044691</v>
+        <v>-0.2670390479360448</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.980494686544181</v>
+        <v>2.979636232445236</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.287101989532598</v>
+        <v>-3.288532746364174</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.820768499736333</v>
+        <v>1.820196197003703</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6232586413428172</v>
+        <v>-0.6246893981743928</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.76201053505743</v>
+        <v>2.761152080958484</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.293762929754746</v>
+        <v>-3.295193686586321</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.819877050347734</v>
+        <v>1.819304747615103</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6232586413428172</v>
+        <v>-0.6246893981743928</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.76378346175769</v>
+        <v>2.762925007658744</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.725568722904534</v>
+        <v>-3.726999479736109</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.633487620555223</v>
+        <v>1.632915317822593</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7596761377840842</v>
+        <v>-0.7611068946156598</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.668265851360334</v>
+        <v>2.667407397261388</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.052001251772277</v>
+        <v>-4.053432008603853</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.491199384010216</v>
+        <v>1.490627081277586</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8421443882912323</v>
+        <v>-0.843575145122808</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.607069676058135</v>
+        <v>2.60621122195919</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.05356540288258</v>
+        <v>-4.054996159714156</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.48915431522206</v>
+        <v>1.48858201248943</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8421443882912323</v>
+        <v>-0.843575145122808</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6056502677141</v>
+        <v>2.604791813615155</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.417191647782894</v>
+        <v>-4.418622404614469</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.350191377496176</v>
+        <v>1.349619074763546</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9403660251583581</v>
+        <v>-0.9417967819899338</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.553204845828067</v>
+        <v>2.552346391729121</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.414764583254176</v>
+        <v>-4.416195340085751</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.350416718313495</v>
+        <v>1.349844415580865</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9406988069655098</v>
+        <v>-0.9421295637970855</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.552259691749607</v>
+        <v>2.551401237650662</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.823353360434854</v>
+        <v>-4.82478411726643</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.185742751455983</v>
+        <v>1.185170448723352</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.305867969455959</v>
+        <v>2.305009515357014</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.236335844575948</v>
+        <v>-5.237766601407523</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.015735190271006</v>
+        <v>1.015162887538375</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.30105340192742</v>
+        <v>2.300194947828474</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.652727718862946</v>
+        <v>-5.654158475694521</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8471724911650842</v>
+        <v>0.8466001884324537</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.299047452536297</v>
+        <v>2.298188998437352</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.02940472939279</v>
+        <v>-6.030835486224365</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7067603776218254</v>
+        <v>0.7061880748891949</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.309306143204976</v>
+        <v>2.308447689106031</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.043119593717901</v>
+        <v>-6.044550350549477</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6973739970374759</v>
+        <v>0.6968016943048454</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.305405708350671</v>
+        <v>2.304547254251726</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.355944392962881</v>
+        <v>-6.357375149794456</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.570648997394485</v>
+        <v>0.5700766946618545</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.350718340977764</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.303810628405672</v>
+        <v>2.302952174306727</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.360757431428218</v>
+        <v>-6.362188188259793</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5725027579375586</v>
+        <v>0.571930455204928</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.35226497568055</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.306661623513209</v>
+        <v>2.305803169414264</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.794106539538454</v>
+        <v>-6.795537296370029</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3951368101590607</v>
+        <v>0.3945645074264306</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.35226497568055</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.302635318978806</v>
+        <v>2.30177686487986</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.177107928281085</v>
+        <v>-7.17853868511266</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2418341533404242</v>
+        <v>0.2412618506077937</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.35226497568055</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.302533217657222</v>
+        <v>2.301674763558276</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.552093254452362</v>
+        <v>-7.553524011283938</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09441153884334375</v>
+        <v>0.09383923611071321</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.725819545020251</v>
+        <v>-1.727250301851827</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.080113537925885</v>
+        <v>2.07925508382694</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.911623576956364</v>
+        <v>-7.913054333787939</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04405028686020707</v>
+        <v>-0.04462258959283716</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.725819545020251</v>
+        <v>-1.727250301851827</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.085463841223936</v>
+        <v>2.08460538712499</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.238023605621377</v>
+        <v>-8.239454362452953</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1666942783690346</v>
+        <v>-0.1672665811016651</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.052219573685264</v>
+        <v>-2.05365033051684</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.897539843982105</v>
+        <v>1.89668138988316</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.231547458827817</v>
+        <v>-8.232978215659394</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1610620690298421</v>
+        <v>-0.1616343717624722</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.045743426891705</v>
+        <v>-2.04717418372328</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.90446728268001</v>
+        <v>1.903608828581065</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.227856533871407</v>
+        <v>-8.229287290702983</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1595856990472777</v>
+        <v>-0.1601580017799082</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.045743426891705</v>
+        <v>-2.04717418372328</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.90446728268001</v>
+        <v>1.903608828581065</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.43211470920127</v>
+        <v>-8.433545466032847</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2357757720605806</v>
+        <v>-0.2363480747932112</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.173382371505693</v>
+        <v>-2.174813128337269</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.833397113030259</v>
+        <v>1.832538658931314</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.381086863119444</v>
+        <v>-8.38251761995102</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2108820791434143</v>
+        <v>-0.2114543818760448</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.098173033198592</v>
+        <v>-2.099603790030168</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.883005270498956</v>
+        <v>1.88214681640001</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.307617031451995</v>
+        <v>-8.309047788283571</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1661224449830137</v>
+        <v>-0.1666947477156437</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.024703201531144</v>
+        <v>-2.02613395836272</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.942458870992846</v>
+        <v>1.941600416893901</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.227244675988066</v>
+        <v>-8.228675432819642</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1194182820499252</v>
+        <v>-0.1199905847825553</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.944330846067214</v>
+        <v>-1.94576160289879</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.00523750501872</v>
+        <v>2.004379050919775</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.415517478353911</v>
+        <v>-8.416948235185487</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2019465678978589</v>
+        <v>-0.2025188706304895</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.944330846067214</v>
+        <v>-1.94576160289879</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.998018340117125</v>
+        <v>1.997159886018179</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.435682119903458</v>
+        <v>-8.437112876735034</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2166846152916539</v>
+        <v>-0.2172569180242845</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.964495487616762</v>
+        <v>-1.965926244448337</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.97924736441342</v>
+        <v>1.978388910314474</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.665506567067283</v>
+        <v>-8.666937323898859</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3074986043186274</v>
+        <v>-0.3080709070512579</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.127143024686922</v>
+        <v>-2.128573781518498</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.88277463200988</v>
+        <v>1.881916177910935</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.602437334760943</v>
+        <v>-8.603868091592519</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2795771827669769</v>
+        <v>-0.2801494854996074</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.157087344200732</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.868360223029654</v>
+        <v>1.867501768930709</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.550421820792129</v>
+        <v>-8.551852577623706</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.2547806414930509</v>
+        <v>-0.255352944225681</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.157087344200732</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.872350558716055</v>
+        <v>1.871492104617109</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628915</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.631713750346334</v>
+        <v>-8.63314450717791</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.288772640213474</v>
+        <v>-0.2893449429461046</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.157087344200732</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.870875331817313</v>
+        <v>1.870016877718368</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410712</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.434444344618337</v>
+        <v>-8.435875101449913</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1948114677574031</v>
+        <v>-0.1953837704900336</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.958387181641158</v>
+        <v>-1.959817938472734</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.004290385418984</v>
+        <v>2.003431931320039</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.235292237381238</v>
+        <v>-8.236722994212814</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.1282017585092463</v>
+        <v>-0.1287740612418768</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.793064655691345</v>
+        <v>-1.794495412522921</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.09043276734219</v>
+        <v>2.089574313243244</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085275</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.009447084661826</v>
+        <v>-8.010877841493404</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.02828462438527302</v>
+        <v>-0.028856927117904</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.751137980104181</v>
+        <v>-1.752568736935757</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.125167845730696</v>
+        <v>2.124309391631751</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.723172272339132</v>
+        <v>-7.72460302917071</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.08736444509986363</v>
+        <v>0.08679214236723221</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.751137980104181</v>
+        <v>-1.752568736935757</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.126306990286755</v>
+        <v>2.12544853618781</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116212</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.496376445265797</v>
+        <v>-7.497807202097375</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1807165500913048</v>
+        <v>0.1801442473586738</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.683024035482637</v>
+        <v>-1.684454792314213</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.169809131221789</v>
+        <v>2.168950677122844</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.212467714337048</v>
+        <v>-7.213898471168626</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.300013746701441</v>
+        <v>0.29944144396881</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.683024035482637</v>
+        <v>-1.684454792314213</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.175542835460426</v>
+        <v>2.17468438136148</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425323</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.965480464144096</v>
+        <v>-6.966911220975674</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3890713843847569</v>
+        <v>0.3884990816521254</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.437467542121261</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.313997923182332</v>
+        <v>2.313139469083386</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.701643596940027</v>
+        <v>-6.703074353771605</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4847226499534769</v>
+        <v>0.4841503472208455</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.437467542121261</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.304114441869424</v>
+        <v>2.303255987770479</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.43440179607163</v>
+        <v>-6.435832552903208</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5897848098014618</v>
+        <v>0.5892125070688308</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.437467542121261</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.302279881370051</v>
+        <v>2.301421427271105</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.158592632671146</v>
+        <v>-6.160023389502724</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6998081601881947</v>
+        <v>0.6992358574555633</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.347017477010951</v>
+        <v>-1.348448233842527</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.35539115136383</v>
+        <v>2.354532697264884</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.889525044904167</v>
+        <v>-5.890955801735744</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.8081037014404799</v>
+        <v>0.807531398707849</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.077949889243972</v>
+        <v>-1.079380646075548</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.517500210169511</v>
+        <v>2.516641756070566</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.625465106581371</v>
+        <v>-5.626895863412948</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.9004673606078462</v>
+        <v>0.8998950578752152</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.8138899509211759</v>
+        <v>-0.8153207077527516</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.662675857001437</v>
+        <v>2.661817402902491</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.918385483076532</v>
+        <v>-4.91981623990811</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.180512176349481</v>
+        <v>1.17993987361685</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.8138899509211759</v>
+        <v>-0.8153207077527516</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.659888823341136</v>
+        <v>2.65903036924219</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.66874445309058</v>
+        <v>-4.670175209922158</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.280712212231703</v>
+        <v>1.280139909499072</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.5642489209352242</v>
+        <v>-0.5656796777667998</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.810017065220548</v>
+        <v>2.809158611121603</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.414202553749504</v>
+        <v>-4.415633310581082</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.38189579318889</v>
+        <v>1.381323490456259</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.3097070215941486</v>
+        <v>-0.3111377784257243</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.96210902604595</v>
+        <v>2.961250571947005</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.180721331519906</v>
+        <v>-4.182152088351484</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.483212710918582</v>
+        <v>1.482640408185951</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.0762257993645501</v>
+        <v>-0.07765655619612577</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.110122188221562</v>
+        <v>3.109263734122616</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.001012801376033</v>
+        <v>-4.002443558207611</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.552203912663172</v>
+        <v>1.551631609930541</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.01905429520185398</v>
+        <v>-0.02048505203342965</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.141532880406221</v>
+        <v>3.140674426307275</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860422</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.868737327745147</v>
+        <v>-3.870168084576725</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.600481588862553</v>
+        <v>1.599909286129922</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.1132211784290327</v>
+        <v>0.111790421597457</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.21626565133178</v>
+        <v>3.215407197232834</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575947</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.678137653071994</v>
+        <v>-3.679568409903572</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.679536519419451</v>
+        <v>1.67896421668682</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.3038208531021855</v>
+        <v>0.3023900962706099</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.333440516823308</v>
+        <v>3.332582062724363</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430981</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.429137854388414</v>
+        <v>-3.430568611219992</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.792042780116542</v>
+        <v>1.791470477383911</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.5528206517857662</v>
+        <v>0.5513898949541906</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.495746737257115</v>
+        <v>3.494888283158169</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077638</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.237758779527474</v>
+        <v>-3.239189536359051</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.7406184804617</v>
+        <v>1.740046177729068</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.7441997266467063</v>
+        <v>0.7427689698151306</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.48259825257446</v>
+        <v>3.481739798475515</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.958731483871847</v>
+        <v>-2.960162240703425</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.900773740601037</v>
+        <v>1.900201437868406</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.7441997266467063</v>
+        <v>0.7427689698151306</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.531142594451547</v>
+        <v>3.530284140352601</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.681993309201034</v>
+        <v>-2.683424066032612</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.014848022455356</v>
+        <v>2.014275719722725</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.9260163877566321</v>
+        <v>0.9245856309250564</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.643611603103497</v>
+        <v>3.642753149004551</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,45 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.409677455812272</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.555100902765965</v>
+        <v>-2.558583043583538</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.056890998775906</v>
+        <v>2.055498142448877</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.052908794191702</v>
+        <v>1.04942665337413</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.711033060711061</v>
+        <v>3.708943776220518</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="2" t="n">
+        <v>45374</v>
+      </c>
+      <c r="B1912" t="n">
+        <v>3.397696173924518</v>
+      </c>
+      <c r="C1912" t="n">
+        <v>2.82229446305379</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>-2.558583043583538</v>
+      </c>
+      <c r="E1912" t="n">
+        <v>2.055498142448877</v>
+      </c>
+      <c r="F1912" t="n">
+        <v>1.04942665337413</v>
+      </c>
+      <c r="G1912" t="n">
+        <v>2.815358260040158</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.9%</t>
+          <t>-566.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>649.6%</t>
+          <t>645.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.4%</t>
+          <t>-417.1%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-227.2%</t>
+          <t>-227.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.7%</t>
+          <t>-170.5%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-308.4%</t>
+          <t>-308.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-119.1%</t>
+          <t>-118.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-185.4%</t>
+          <t>-185.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -43687,16 +43687,16 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>0.9719539229773715</v>
+        <v>0.9733846798089471</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.518494423967709</v>
+        <v>3.51906672670034</v>
       </c>
       <c r="F1832" t="n">
-        <v>1.945818843285647</v>
+        <v>1.947249600117223</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.297560585061897</v>
+        <v>4.298419039160843</v>
       </c>
     </row>
     <row r="1833">
@@ -43710,16 +43710,16 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>0.9241155607311727</v>
+        <v>0.9255463175627483</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.496231132970942</v>
+        <v>3.496803435703573</v>
       </c>
       <c r="F1833" t="n">
-        <v>1.945818843285647</v>
+        <v>1.947249600117223</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.294432638963609</v>
+        <v>4.295291093062554</v>
       </c>
     </row>
     <row r="1834">
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.588172593222843</v>
+        <v>0.5896033500544184</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.374830555251</v>
+        <v>3.37540285798363</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.609875875777317</v>
+        <v>1.611306632608893</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.105843467742001</v>
+        <v>4.106701921840946</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5876207933810308</v>
+        <v>0.5890515502126062</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.372867671176619</v>
+        <v>3.37343997390925</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.610717639262624</v>
+        <v>1.612148396094199</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.104606361695529</v>
+        <v>4.105464815794474</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4819339054387311</v>
+        <v>0.4833646622703066</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.310418188627147</v>
+        <v>3.310990491359777</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.59615656555994</v>
+        <v>1.597587322391516</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.075694990101367</v>
+        <v>4.076553444200312</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4877832865539755</v>
+        <v>0.4892140433855509</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.313247079799119</v>
+        <v>3.313819382531749</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.59615656555994</v>
+        <v>1.597587322391516</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.07618412882724</v>
+        <v>4.077042582926186</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4395610197068919</v>
+        <v>0.4409917765384674</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.298038155681952</v>
+        <v>3.298610458414582</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.547934298712857</v>
+        <v>1.549365055544432</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.051330751340657</v>
+        <v>4.052189205439602</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2024295278570968</v>
+        <v>0.2038602846886723</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.238126643439576</v>
+        <v>3.238698946172206</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.547934298712857</v>
+        <v>1.549365055544432</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.086271835838199</v>
+        <v>4.087130289937144</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2074671185846834</v>
+        <v>0.2088978754162588</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.238719119915948</v>
+        <v>3.239291422648579</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.603578754979174</v>
+        <v>1.60500951181075</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.118235949783327</v>
+        <v>4.119094403882272</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1509974874083866</v>
+        <v>0.152428244239962</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.194877649069167</v>
+        <v>3.195449951801797</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.547109123802877</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.063100552701286</v>
+        <v>4.063959006800231</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08523009735897452</v>
+        <v>0.08666085419054997</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.169588302179872</v>
+        <v>3.170160604912502</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.547109123802877</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.064118161831756</v>
+        <v>4.064976615930702</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07169461358226492</v>
+        <v>0.07312537041384037</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.154802140656944</v>
+        <v>3.155374443389574</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.547109123802877</v>
+        <v>1.548539880634453</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.054746193819511</v>
+        <v>4.055604647918457</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.01007728684548675</v>
+        <v>-0.008646530013911302</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.112176106441082</v>
+        <v>3.112748409173712</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.574144697209014</v>
+        <v>1.575575454040589</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.061050263818432</v>
+        <v>4.061908717917378</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07728639471736443</v>
+        <v>-0.07585563788578897</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.090057780126033</v>
+        <v>3.090630082858663</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.574144697209014</v>
+        <v>1.575575454040589</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.065815580652134</v>
+        <v>4.066674034751079</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.07329494192217423</v>
+        <v>-0.07186418509059878</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.089479157363349</v>
+        <v>3.090051460095979</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.578136150004204</v>
+        <v>1.57956690683578</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.066035248448489</v>
+        <v>4.066893702547434</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4714433728754349</v>
+        <v>-0.4700126160438594</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.928146676487108</v>
+        <v>2.928718979219738</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.179987719050943</v>
+        <v>1.181418475882519</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.825073081381595</v>
+        <v>3.825931535480541</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6930653064335524</v>
+        <v>-0.6916345496019769</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.839364119662783</v>
+        <v>2.839936422395413</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.142461585363574</v>
+        <v>1.14389234219515</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.802423617768096</v>
+        <v>3.803282071867041</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9010693647866296</v>
+        <v>-0.8996386079550541</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.761054640875477</v>
+        <v>2.761626943608107</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.142461585363574</v>
+        <v>1.14389234219515</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.807315762322021</v>
+        <v>3.808174216420967</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.171469327495515</v>
+        <v>-1.170038570663939</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.647976112129911</v>
+        <v>2.648548414862542</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8720616226546889</v>
+        <v>0.8734923794862646</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.640157241034678</v>
+        <v>3.641015695133623</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.510627705084037</v>
+        <v>-1.509196948252461</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.505397060400951</v>
+        <v>2.505969363133582</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5329032450661668</v>
+        <v>0.5343340018977425</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.429746513788014</v>
+        <v>3.430604967886959</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.838644926811516</v>
+        <v>-1.83721416997994</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.394528461448728</v>
+        <v>2.395100764181358</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2048860233386877</v>
+        <v>0.2063167801702633</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.253274470490295</v>
+        <v>3.25413292458924</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.835308180302545</v>
+        <v>-1.833877423470969</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.403961910460885</v>
+        <v>2.404534213193516</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.207578055757719</v>
+        <v>0.2090088125892947</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.262988440350282</v>
+        <v>3.263846894449228</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.20201923196909</v>
+        <v>-2.200588475137515</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.258383881837999</v>
+        <v>2.258956184570629</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1591329959088266</v>
+        <v>-0.1577022390772509</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.044068201394087</v>
+        <v>3.044926655493033</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.587199622899162</v>
+        <v>-2.585768866067587</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.102854264278833</v>
+        <v>2.103426567011464</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1591329959088266</v>
+        <v>-0.1577022390772509</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.04261074020695</v>
+        <v>3.043469194305896</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.930882396125825</v>
+        <v>-2.92945163929425</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.967150278442785</v>
+        <v>1.967722581175415</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2670390479360448</v>
+        <v>-0.2656082911044691</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.979636232445236</v>
+        <v>2.980494686544181</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.288532746364174</v>
+        <v>-3.287101989532598</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.820196197003703</v>
+        <v>1.820768499736333</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6246893981743928</v>
+        <v>-0.6232586413428172</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.761152080958484</v>
+        <v>2.76201053505743</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.295193686586321</v>
+        <v>-3.293762929754746</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.819304747615103</v>
+        <v>1.819877050347734</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6246893981743928</v>
+        <v>-0.6232586413428172</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.762925007658744</v>
+        <v>2.76378346175769</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.726999479736109</v>
+        <v>-3.725568722904534</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.632915317822593</v>
+        <v>1.633487620555223</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7611068946156598</v>
+        <v>-0.7596761377840842</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.667407397261388</v>
+        <v>2.668265851360334</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.053432008603853</v>
+        <v>-4.052001251772277</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.490627081277586</v>
+        <v>1.491199384010216</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.843575145122808</v>
+        <v>-0.8421443882912323</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.60621122195919</v>
+        <v>2.607069676058135</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.054996159714156</v>
+        <v>-4.05356540288258</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.48858201248943</v>
+        <v>1.48915431522206</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.843575145122808</v>
+        <v>-0.8421443882912323</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.604791813615155</v>
+        <v>2.6056502677141</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.418622404614469</v>
+        <v>-4.417191647782894</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.349619074763546</v>
+        <v>1.350191377496176</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9417967819899338</v>
+        <v>-0.9403660251583581</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.552346391729121</v>
+        <v>2.553204845828067</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.416195340085751</v>
+        <v>-4.414764583254176</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.349844415580865</v>
+        <v>1.350416718313495</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9421295637970855</v>
+        <v>-0.9406988069655098</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.551401237650662</v>
+        <v>2.552259691749607</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.82478411726643</v>
+        <v>-4.823353360434854</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.185170448723352</v>
+        <v>1.185742751455983</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.305009515357014</v>
+        <v>2.305867969455959</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.237766601407523</v>
+        <v>-5.236335844575948</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.015162887538375</v>
+        <v>1.015735190271006</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.300194947828474</v>
+        <v>2.30105340192742</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.654158475694521</v>
+        <v>-5.652727718862946</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8466001884324537</v>
+        <v>0.8471724911650842</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.298188998437352</v>
+        <v>2.299047452536297</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.030835486224365</v>
+        <v>-6.02940472939279</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7061880748891949</v>
+        <v>0.7067603776218254</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.308447689106031</v>
+        <v>2.309306143204976</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.044550350549477</v>
+        <v>-6.043119593717901</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6968016943048454</v>
+        <v>0.6973739970374759</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.304547254251726</v>
+        <v>2.305405708350671</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.357375149794456</v>
+        <v>-6.355944392962881</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5700766946618545</v>
+        <v>0.570648997394485</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.350718340977764</v>
+        <v>-1.349287584146188</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.302952174306727</v>
+        <v>2.303810628405672</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.362188188259793</v>
+        <v>-6.360757431428218</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.571930455204928</v>
+        <v>0.5725027579375586</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.35226497568055</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.305803169414264</v>
+        <v>2.306661623513209</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.795537296370029</v>
+        <v>-6.794106539538454</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3945645074264306</v>
+        <v>0.3951368101590607</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.35226497568055</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.30177686487986</v>
+        <v>2.302635318978806</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.17853868511266</v>
+        <v>-7.177107928281085</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2412618506077937</v>
+        <v>0.2418341533404242</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.35226497568055</v>
+        <v>-1.350834218848974</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.301674763558276</v>
+        <v>2.302533217657222</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.553524011283938</v>
+        <v>-7.552093254452362</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09383923611071321</v>
+        <v>0.09441153884334375</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.727250301851827</v>
+        <v>-1.725819545020251</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.07925508382694</v>
+        <v>2.080113537925885</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.913054333787939</v>
+        <v>-7.911623576956364</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04462258959283716</v>
+        <v>-0.04405028686020707</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.727250301851827</v>
+        <v>-1.725819545020251</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.08460538712499</v>
+        <v>2.085463841223936</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.239454362452953</v>
+        <v>-8.238023605621377</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1672665811016651</v>
+        <v>-0.1666942783690346</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.05365033051684</v>
+        <v>-2.052219573685264</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.89668138988316</v>
+        <v>1.897539843982105</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.232978215659394</v>
+        <v>-8.231547458827817</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1616343717624722</v>
+        <v>-0.1610620690298421</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.04717418372328</v>
+        <v>-2.045743426891705</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.903608828581065</v>
+        <v>1.90446728268001</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.229287290702983</v>
+        <v>-8.227856533871407</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1601580017799082</v>
+        <v>-0.1595856990472777</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.04717418372328</v>
+        <v>-2.045743426891705</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.903608828581065</v>
+        <v>1.90446728268001</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.433545466032847</v>
+        <v>-8.43211470920127</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2363480747932112</v>
+        <v>-0.2357757720605806</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.174813128337269</v>
+        <v>-2.173382371505693</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.832538658931314</v>
+        <v>1.833397113030259</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.38251761995102</v>
+        <v>-8.381086863119444</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2114543818760448</v>
+        <v>-0.2108820791434143</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.099603790030168</v>
+        <v>-2.098173033198592</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.88214681640001</v>
+        <v>1.883005270498956</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.309047788283571</v>
+        <v>-8.307617031451995</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1666947477156437</v>
+        <v>-0.1661224449830137</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.02613395836272</v>
+        <v>-2.024703201531144</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.941600416893901</v>
+        <v>1.942458870992846</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.228675432819642</v>
+        <v>-8.227244675988066</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1199905847825553</v>
+        <v>-0.1194182820499252</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.94576160289879</v>
+        <v>-1.944330846067214</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.004379050919775</v>
+        <v>2.00523750501872</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.416948235185487</v>
+        <v>-8.415517478353911</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2025188706304895</v>
+        <v>-0.2019465678978589</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.94576160289879</v>
+        <v>-1.944330846067214</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.997159886018179</v>
+        <v>1.998018340117125</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.437112876735034</v>
+        <v>-8.435682119903458</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2172569180242845</v>
+        <v>-0.2166846152916539</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.965926244448337</v>
+        <v>-1.964495487616762</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.978388910314474</v>
+        <v>1.97924736441342</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.666937323898859</v>
+        <v>-8.665506567067283</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3080709070512579</v>
+        <v>-0.3074986043186274</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.128573781518498</v>
+        <v>-2.127143024686922</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.881916177910935</v>
+        <v>1.88277463200988</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.603868091592519</v>
+        <v>-8.602437334760943</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2801494854996074</v>
+        <v>-0.2795771827669769</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.157087344200732</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.867501768930709</v>
+        <v>1.868360223029654</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.551852577623706</v>
+        <v>-8.550421820792129</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.255352944225681</v>
+        <v>-0.2547806414930509</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.157087344200732</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.871492104617109</v>
+        <v>1.872350558716055</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.63314450717791</v>
+        <v>-8.631713750346334</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.2893449429461046</v>
+        <v>-0.288772640213474</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.157087344200732</v>
+        <v>-2.155656587369156</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.870016877718368</v>
+        <v>1.870875331817313</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.435875101449913</v>
+        <v>-8.434444344618337</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1953837704900336</v>
+        <v>-0.1948114677574031</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.959817938472734</v>
+        <v>-1.958387181641158</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.003431931320039</v>
+        <v>2.004290385418984</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.236722994212814</v>
+        <v>-8.235292237381238</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.1287740612418768</v>
+        <v>-0.1282017585092463</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.794495412522921</v>
+        <v>-1.793064655691345</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.089574313243244</v>
+        <v>2.09043276734219</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.010877841493404</v>
+        <v>-8.009447084661826</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.028856927117904</v>
+        <v>-0.02828462438527302</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.752568736935757</v>
+        <v>-1.751137980104181</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.124309391631751</v>
+        <v>2.125167845730696</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.72460302917071</v>
+        <v>-7.723172272339132</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.08679214236723221</v>
+        <v>0.08736444509986363</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.752568736935757</v>
+        <v>-1.751137980104181</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.12544853618781</v>
+        <v>2.126306990286755</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.497807202097375</v>
+        <v>-7.496376445265797</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1801442473586738</v>
+        <v>0.1807165500913048</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.684454792314213</v>
+        <v>-1.683024035482637</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.168950677122844</v>
+        <v>2.169809131221789</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.213898471168626</v>
+        <v>-7.212467714337048</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.29944144396881</v>
+        <v>0.300013746701441</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.684454792314213</v>
+        <v>-1.683024035482637</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.17468438136148</v>
+        <v>2.175542835460426</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.966911220975674</v>
+        <v>-6.965480464144096</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3884990816521254</v>
+        <v>0.3890713843847569</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.437467542121261</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.313139469083386</v>
+        <v>2.313997923182332</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.703074353771605</v>
+        <v>-6.701643596940027</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4841503472208455</v>
+        <v>0.4847226499534769</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.437467542121261</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.303255987770479</v>
+        <v>2.304114441869424</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.435832552903208</v>
+        <v>-6.43440179607163</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5892125070688308</v>
+        <v>0.5897848098014618</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.437467542121261</v>
+        <v>-1.436036785289685</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.301421427271105</v>
+        <v>2.302279881370051</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.160023389502724</v>
+        <v>-6.158592632671146</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6992358574555633</v>
+        <v>0.6998081601881947</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.348448233842527</v>
+        <v>-1.347017477010951</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.354532697264884</v>
+        <v>2.35539115136383</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.890955801735744</v>
+        <v>-5.889525044904167</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.807531398707849</v>
+        <v>0.8081037014404799</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.079380646075548</v>
+        <v>-1.077949889243972</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.516641756070566</v>
+        <v>2.517500210169511</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.626895863412948</v>
+        <v>-5.625465106581371</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8998950578752152</v>
+        <v>0.9004673606078462</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.8153207077527516</v>
+        <v>-0.8138899509211759</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.661817402902491</v>
+        <v>2.662675857001437</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.91981623990811</v>
+        <v>-4.918385483076532</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.17993987361685</v>
+        <v>1.180512176349481</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.8153207077527516</v>
+        <v>-0.8138899509211759</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.65903036924219</v>
+        <v>2.659888823341136</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.670175209922158</v>
+        <v>-4.66874445309058</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.280139909499072</v>
+        <v>1.280712212231703</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.5656796777667998</v>
+        <v>-0.5642489209352242</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.809158611121603</v>
+        <v>2.810017065220548</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.415633310581082</v>
+        <v>-4.414202553749504</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.381323490456259</v>
+        <v>1.38189579318889</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.3111377784257243</v>
+        <v>-0.3097070215941486</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.961250571947005</v>
+        <v>2.96210902604595</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.182152088351484</v>
+        <v>-4.180721331519906</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.482640408185951</v>
+        <v>1.483212710918582</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.07765655619612577</v>
+        <v>-0.0762257993645501</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.109263734122616</v>
+        <v>3.110122188221562</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.002443558207611</v>
+        <v>-4.001012801376033</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.551631609930541</v>
+        <v>1.552203912663172</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.02048505203342965</v>
+        <v>-0.01905429520185398</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.140674426307275</v>
+        <v>3.141532880406221</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.870168084576725</v>
+        <v>-3.868737327745147</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.599909286129922</v>
+        <v>1.600481588862553</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.111790421597457</v>
+        <v>0.1132211784290327</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.215407197232834</v>
+        <v>3.21626565133178</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.679568409903572</v>
+        <v>-3.678137653071994</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.67896421668682</v>
+        <v>1.679536519419451</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.3023900962706099</v>
+        <v>0.3038208531021855</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.332582062724363</v>
+        <v>3.333440516823308</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.430568611219992</v>
+        <v>-3.429137854388414</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.791470477383911</v>
+        <v>1.792042780116542</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.5513898949541906</v>
+        <v>0.5528206517857662</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.494888283158169</v>
+        <v>3.495746737257115</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.239189536359051</v>
+        <v>-3.237758779527474</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.740046177729068</v>
+        <v>1.7406184804617</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.7427689698151306</v>
+        <v>0.7441997266467063</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.481739798475515</v>
+        <v>3.48259825257446</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.960162240703425</v>
+        <v>-2.958731483871847</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.900201437868406</v>
+        <v>1.900773740601037</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.7427689698151306</v>
+        <v>0.7441997266467063</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.530284140352601</v>
+        <v>3.531142594451547</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.683424066032612</v>
+        <v>-2.681993309201034</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.014275719722725</v>
+        <v>2.014848022455356</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.9245856309250564</v>
+        <v>0.9260163877566321</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.642753149004551</v>
+        <v>3.643611603103497</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.558583043583538</v>
+        <v>-2.555100902765965</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.055498142448877</v>
+        <v>2.056890998775906</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.04942665337413</v>
+        <v>1.052908794191702</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.708943776220518</v>
+        <v>3.711033060711061</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,13 +45527,13 @@
         <v>2.82229446305379</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.558583043583538</v>
+        <v>-2.555100902765965</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.055498142448877</v>
+        <v>2.056890998775906</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.04942665337413</v>
+        <v>1.052908794191702</v>
       </c>
       <c r="G1912" t="n">
         <v>2.815358260040158</v>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-68.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.7%</t>
+          <t>-62.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>645.8%</t>
+          <t>646.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.1%</t>
+          <t>-422.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-36.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.5%</t>
+          <t>-173.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-160.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-118.7%</t>
+          <t>-120.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-76.6%</t>
         </is>
       </c>
     </row>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.381086863119444</v>
+        <v>-8.624612723319617</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2108820791434143</v>
+        <v>-0.3082924232234832</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.098173033198592</v>
+        <v>-2.304495339094012</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.883005270498956</v>
+        <v>1.759211886961704</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.307617031451995</v>
+        <v>-8.551142891652168</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1661224449830137</v>
+        <v>-0.2635327890630825</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.024703201531144</v>
+        <v>-2.231025507426563</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.942458870992846</v>
+        <v>1.818665487455594</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.227244675988066</v>
+        <v>-8.470770536188239</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1194182820499252</v>
+        <v>-0.2168286261299941</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.944330846067214</v>
+        <v>-2.150653151962634</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.00523750501872</v>
+        <v>1.881444121481469</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.415517478353911</v>
+        <v>-8.659043338554083</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2019465678978589</v>
+        <v>-0.2993569119779278</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.944330846067214</v>
+        <v>-2.150653151962634</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.998018340117125</v>
+        <v>1.874224956579873</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.435682119903458</v>
+        <v>-8.67920798010363</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2166846152916539</v>
+        <v>-0.3140949593717228</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.964495487616762</v>
+        <v>-2.170817793512181</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.97924736441342</v>
+        <v>1.855453980876168</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.665506567067283</v>
+        <v>-8.909032427267455</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3074986043186274</v>
+        <v>-0.4049089483986963</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.127143024686922</v>
+        <v>-2.333465330582342</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.88277463200988</v>
+        <v>1.758981248472628</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.602437334760943</v>
+        <v>-8.845963194961115</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2795771827669769</v>
+        <v>-0.3769875268470457</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.361978893264576</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.868360223029654</v>
+        <v>1.744566839492402</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.550421820792129</v>
+        <v>-8.793947680992302</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.2547806414930509</v>
+        <v>-0.3521909855731198</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.361978893264576</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.872350558716055</v>
+        <v>1.748557175178803</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.631713750346334</v>
+        <v>-8.875239610546506</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.288772640213474</v>
+        <v>-0.3861829842935434</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.155656587369156</v>
+        <v>-2.361978893264576</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.870875331817313</v>
+        <v>1.747081948280061</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.434444344618337</v>
+        <v>-8.677970204818509</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1948114677574031</v>
+        <v>-0.292221811837472</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.958387181641158</v>
+        <v>-2.164709487536578</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.004290385418984</v>
+        <v>1.880497001881732</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.235292237381238</v>
+        <v>-8.47881809758141</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.1282017585092463</v>
+        <v>-0.2256121025893152</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.793064655691345</v>
+        <v>-1.999386961586765</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.09043276734219</v>
+        <v>1.966639383804937</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.009447084661826</v>
+        <v>-8.252972944861998</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.02828462438527302</v>
+        <v>-0.1256949684653419</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.751137980104181</v>
+        <v>-1.957460285999601</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.125167845730696</v>
+        <v>2.001374462193445</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.723172272339132</v>
+        <v>-7.966698132539304</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.08736444509986363</v>
+        <v>-0.01004589898020525</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.751137980104181</v>
+        <v>-1.957460285999601</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.126306990286755</v>
+        <v>2.002513606749504</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.496376445265797</v>
+        <v>-7.73990230546597</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1807165500913048</v>
+        <v>0.08330620601123595</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.683024035482637</v>
+        <v>-1.889346341378057</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.169809131221789</v>
+        <v>2.046015747684538</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.212467714337048</v>
+        <v>-7.455993574537221</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.300013746701441</v>
+        <v>0.2026034026213721</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.683024035482637</v>
+        <v>-1.889346341378057</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.175542835460426</v>
+        <v>2.051749451923174</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.965480464144096</v>
+        <v>-7.209006324344268</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3890713843847569</v>
+        <v>0.291661040304688</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.642359091185105</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.313997923182332</v>
+        <v>2.19020453964508</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.701643596940027</v>
+        <v>-6.945169457140199</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4847226499534769</v>
+        <v>0.3873123058734076</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.642359091185105</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.304114441869424</v>
+        <v>2.180321058332172</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.43440179607163</v>
+        <v>-6.677927656271803</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5897848098014618</v>
+        <v>0.4923744657213929</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.436036785289685</v>
+        <v>-1.642359091185105</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.302279881370051</v>
+        <v>2.178486497832798</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.158592632671146</v>
+        <v>-6.402118492871319</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6998081601881947</v>
+        <v>0.6023978161081254</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.347017477010951</v>
+        <v>-1.553339782906371</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.35539115136383</v>
+        <v>2.231597767826578</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.889525044904167</v>
+        <v>-6.133050905104339</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.8081037014404799</v>
+        <v>0.7106933573604111</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.077949889243972</v>
+        <v>-1.284272195139392</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.517500210169511</v>
+        <v>2.393706826632259</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.625465106581371</v>
+        <v>-5.868990966781543</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.9004673606078462</v>
+        <v>0.8030570165277773</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.8138899509211759</v>
+        <v>-1.020212256816596</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.662675857001437</v>
+        <v>2.538882473464185</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.918385483076532</v>
+        <v>-5.161911343276705</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.180512176349481</v>
+        <v>1.083101832269412</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.8138899509211759</v>
+        <v>-1.020212256816596</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.659888823341136</v>
+        <v>2.536095439803884</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.66874445309058</v>
+        <v>-4.912270313290753</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.280712212231703</v>
+        <v>1.183301868151634</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.5642489209352242</v>
+        <v>-0.7705712268306439</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.810017065220548</v>
+        <v>2.686223681683297</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.414202553749504</v>
+        <v>-4.657728413949677</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.38189579318889</v>
+        <v>1.284485449108821</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.3097070215941486</v>
+        <v>-0.5160293274895684</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.96210902604595</v>
+        <v>2.838315642508698</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.180721331519906</v>
+        <v>-4.424247191720078</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.483212710918582</v>
+        <v>1.385802366838513</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.0762257993645501</v>
+        <v>-0.2825481052599699</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.110122188221562</v>
+        <v>2.98632880468431</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.001012801376033</v>
+        <v>-4.244538661576206</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.552203912663172</v>
+        <v>1.454793568583103</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.01905429520185398</v>
+        <v>-0.2253766010972738</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.141532880406221</v>
+        <v>3.017739496868968</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.868737327745147</v>
+        <v>-4.112263187945319</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.600481588862553</v>
+        <v>1.503071244782485</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.1132211784290327</v>
+        <v>-0.0931011274663871</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.21626565133178</v>
+        <v>3.092472267794527</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.678137653071994</v>
+        <v>-3.921663513272167</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.679536519419451</v>
+        <v>1.582126175339382</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.3038208531021855</v>
+        <v>0.09749854720676576</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.333440516823308</v>
+        <v>3.209647133286056</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.429137854388414</v>
+        <v>-3.672663714588586</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.792042780116542</v>
+        <v>1.694632436036473</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.5528206517857662</v>
+        <v>0.3464983458903464</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.495746737257115</v>
+        <v>3.371953353719863</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.237758779527474</v>
+        <v>-3.481284639727646</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.7406184804617</v>
+        <v>1.643208136381631</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.7441997266467063</v>
+        <v>0.5378774207512865</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.48259825257446</v>
+        <v>3.358804869037209</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.958731483871847</v>
+        <v>-3.202257344072019</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.900773740601037</v>
+        <v>1.803363396520968</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.7441997266467063</v>
+        <v>0.5378774207512865</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.531142594451547</v>
+        <v>3.407349210914295</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.681993309201034</v>
+        <v>-2.925519169401207</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.014848022455356</v>
+        <v>1.917437678375287</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.9260163877566321</v>
+        <v>0.7196940818612123</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.643611603103497</v>
+        <v>3.519818219566245</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.555100902765965</v>
+        <v>-2.798626762966137</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.056890998775906</v>
+        <v>1.959480654695837</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.052908794191702</v>
+        <v>0.8465864882962822</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.711033060711061</v>
+        <v>3.587239677173809</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.397696173924518</v>
+        <v>3.418242935835273</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.82229446305379</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.555100902765965</v>
+        <v>-2.609091719118912</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.056890998775906</v>
+        <v>2.028334060139634</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.052908794191702</v>
+        <v>1.036121532143507</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.815358260040158</v>
+        <v>3.69400009138705</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240323.xlsx
+++ b/tame_output/ON/bt/strategyON_20240323.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-65.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>120.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.8%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-59.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>646.1%</t>
+          <t>498.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-422.5%</t>
+          <t>-392.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-227.1%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-173.4%</t>
+          <t>-161.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-308.2%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.8%</t>
+          <t>-149.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-120.4%</t>
+          <t>-110.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-185.3%</t>
+          <t>-169.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-70.9%</t>
         </is>
       </c>
     </row>
@@ -43687,16 +43687,16 @@
         <v>3.130069279090508</v>
       </c>
       <c r="D1832" t="n">
-        <v>0.9733846798089471</v>
+        <v>1.242410788905723</v>
       </c>
       <c r="E1832" t="n">
-        <v>3.51906672670034</v>
+        <v>3.62667717033905</v>
       </c>
       <c r="F1832" t="n">
-        <v>1.947249600117223</v>
+        <v>2.216275709213999</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.298419039160843</v>
+        <v>4.459834704618908</v>
       </c>
     </row>
     <row r="1833">
@@ -43710,16 +43710,16 @@
         <v>3.12694133299222</v>
       </c>
       <c r="D1833" t="n">
-        <v>0.9255463175627483</v>
+        <v>1.194572426659524</v>
       </c>
       <c r="E1833" t="n">
-        <v>3.496803435703573</v>
+        <v>3.604413879342283</v>
       </c>
       <c r="F1833" t="n">
-        <v>1.947249600117223</v>
+        <v>2.216275709213999</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.295291093062554</v>
+        <v>4.45670675852062</v>
       </c>
     </row>
     <row r="1834">
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.5896033500544184</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.37540285798363</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.611306632608893</v>
+        <v>1.880332741705669</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.106701921840946</v>
+        <v>4.268117587299011</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.5890515502126062</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.37343997390925</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.612148396094199</v>
+        <v>1.881174505190975</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.105464815794474</v>
+        <v>4.26688048125254</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4833646622703066</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.310990491359777</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.597587322391516</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.076553444200312</v>
+        <v>4.237969109658377</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4892140433855509</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.313819382531749</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.597587322391516</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.077042582926186</v>
+        <v>4.238458248384251</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4409917765384674</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.298610458414582</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.549365055544432</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.052189205439602</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2038602846886723</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.238698946172206</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.549365055544432</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.087130289937144</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2088978754162588</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.239291422648579</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.60500951181075</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.119094403882272</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.152428244239962</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.195449951801797</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.548539880634453</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.063959006800231</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08666085419054997</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.170160604912502</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.548539880634453</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.064976615930702</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07312537041384037</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.155374443389574</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.548539880634453</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.055604647918457</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.008646530013911302</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.112748409173712</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.575575454040589</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.061908717917378</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07585563788578897</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.090630082858663</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.575575454040589</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.066674034751079</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.07186418509059878</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.090051460095979</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.57956690683578</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.066893702547434</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4700126160438594</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.928718979219738</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.181418475882519</v>
+        <v>1.450444584979295</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.825931535480541</v>
+        <v>3.987347200938607</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6916345496019769</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.839936422395413</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.14389234219515</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.803282071867041</v>
+        <v>3.964697737325107</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8996386079550541</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.761626943608107</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.14389234219515</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.808174216420967</v>
+        <v>3.969589881879032</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.170038570663939</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.648548414862542</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8734923794862646</v>
+        <v>1.14251848858304</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.641015695133623</v>
+        <v>3.802431360591689</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.509196948252461</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.505969363133582</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5343340018977425</v>
+        <v>0.8033601109945183</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.430604967886959</v>
+        <v>3.592020633345025</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.83721416997994</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.395100764181358</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2063167801702633</v>
+        <v>0.4753428892670392</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.25413292458924</v>
+        <v>3.415548590047305</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.833877423470969</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.404534213193516</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2090088125892947</v>
+        <v>0.4780349216860705</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.263846894449228</v>
+        <v>3.425262559907293</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.200588475137515</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.258956184570629</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1577022390772509</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.044926655493033</v>
+        <v>3.206342320951098</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.585768866067587</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.103426567011464</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1577022390772509</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.043469194305896</v>
+        <v>3.204884859763961</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.92945163929425</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.967722581175415</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2656082911044691</v>
+        <v>0.003417817992306726</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.980494686544181</v>
+        <v>3.141910352002246</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.287101989532598</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.820768499736333</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6232586413428172</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.76201053505743</v>
+        <v>2.923426200515495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.293762929754746</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.819877050347734</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6232586413428172</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.76378346175769</v>
+        <v>2.925199127215755</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.725568722904534</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.633487620555223</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7596761377840842</v>
+        <v>-0.4906500286873084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.668265851360334</v>
+        <v>2.829681516818399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.052001251772277</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.491199384010216</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8421443882912323</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.607069676058135</v>
+        <v>2.768485341516201</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.05356540288258</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.48915431522206</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8421443882912323</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6056502677141</v>
+        <v>2.767065933172166</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.417191647782894</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.350191377496176</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9403660251583581</v>
+        <v>-0.6713399160615824</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.553204845828067</v>
+        <v>2.714620511286132</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.414764583254176</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.350416718313495</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9406988069655098</v>
+        <v>-0.671672697868734</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.552259691749607</v>
+        <v>2.713675357207673</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.823353360434854</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.185742751455983</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.305867969455959</v>
+        <v>2.467283634914025</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.236335844575948</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.015735190271006</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.30105340192742</v>
+        <v>2.462469067385485</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.652727718862946</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8471724911650842</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.299047452536297</v>
+        <v>2.460463117994363</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.02940472939279</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7067603776218254</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.309306143204976</v>
+        <v>2.470721808663042</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.043119593717901</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6973739970374759</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.305405708350671</v>
+        <v>2.466821373808737</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.355944392962881</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.570648997394485</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.349287584146188</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.303810628405672</v>
+        <v>2.465226293863738</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.360757431428218</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5725027579375586</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.306661623513209</v>
+        <v>2.468077288971275</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.794106539538454</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3951368101590607</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.302635318978806</v>
+        <v>2.464050984436871</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.177107928281085</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2418341533404242</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.350834218848974</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.302533217657222</v>
+        <v>2.463948883115287</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.552093254452362</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09441153884334375</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.725819545020251</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.080113537925885</v>
+        <v>2.241529203383951</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.911623576956364</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04405028686020707</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.725819545020251</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.085463841223936</v>
+        <v>2.246879506682001</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.238023605621377</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1666942783690346</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.052219573685264</v>
+        <v>-1.783193464588488</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.897539843982105</v>
+        <v>2.058955509440171</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.231547458827817</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1610620690298421</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.045743426891705</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.90446728268001</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.227856533871407</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1595856990472777</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.045743426891705</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.90446728268001</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.43211470920127</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2357757720605806</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.173382371505693</v>
+        <v>-1.904356262408918</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.833397113030259</v>
+        <v>1.994812778488325</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.624612723319617</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3082924232234832</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.304495339094012</v>
+        <v>-2.019089735411313</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.759211886961704</v>
+        <v>1.930455249171323</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.551142891652168</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2635327890630825</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.231025507426563</v>
+        <v>-1.945619903743865</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.818665487455594</v>
+        <v>1.989908849665214</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.470770536188239</v>
+        <v>-8.169885439461479</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2168286261299941</v>
+        <v>-0.09647458743929027</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.150653151962634</v>
+        <v>-1.865247548279935</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.881444121481469</v>
+        <v>2.052687483691088</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.659043338554083</v>
+        <v>-8.358158241827324</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2993569119779278</v>
+        <v>-0.179002873287224</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.150653151962634</v>
+        <v>-1.865247548279935</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.874224956579873</v>
+        <v>2.045468318789492</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.67920798010363</v>
+        <v>-8.378322883376871</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3140949593717228</v>
+        <v>-0.193740920681019</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.170817793512181</v>
+        <v>-1.885412189829483</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.855453980876168</v>
+        <v>2.026697343085787</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.909032427267455</v>
+        <v>-8.608147330540696</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4049089483986963</v>
+        <v>-0.2845549097079929</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.333465330582342</v>
+        <v>-2.048059726899643</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.758981248472628</v>
+        <v>1.930224610682247</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.845963194961115</v>
+        <v>-8.545078098234356</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3769875268470457</v>
+        <v>-0.2566334881563423</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.361978893264576</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.744566839492402</v>
+        <v>1.915810201702022</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.793947680992302</v>
+        <v>-8.493062584265543</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3521909855731198</v>
+        <v>-0.231836946882416</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.361978893264576</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.748557175178803</v>
+        <v>1.919800537388422</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.875239610546506</v>
+        <v>-8.574354513819747</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3861829842935434</v>
+        <v>-0.2658289456028395</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.361978893264576</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.747081948280061</v>
+        <v>1.91832531048968</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.677970204818509</v>
+        <v>-8.37708510809175</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.292221811837472</v>
+        <v>-0.1718677731467682</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.164709487536578</v>
+        <v>-1.879303883853879</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.880497001881732</v>
+        <v>2.051740364091352</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.47881809758141</v>
+        <v>-8.177933000854651</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2256121025893152</v>
+        <v>-0.1052580638986118</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.999386961586765</v>
+        <v>-1.713981357904066</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.966639383804937</v>
+        <v>2.137882746014557</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.252972944861998</v>
+        <v>-7.95208784813524</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1256949684653419</v>
+        <v>-0.005340929774638514</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.957460285999601</v>
+        <v>-1.672054682316902</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.001374462193445</v>
+        <v>2.172617824403064</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.966698132539304</v>
+        <v>-7.665813035812546</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.01004589898020525</v>
+        <v>0.1103081397104977</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.957460285999601</v>
+        <v>-1.672054682316902</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.002513606749504</v>
+        <v>2.173756968959123</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.73990230546597</v>
+        <v>-7.439017208739212</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.08330620601123595</v>
+        <v>0.2036602447019389</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.889346341378057</v>
+        <v>-1.603940737695358</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.046015747684538</v>
+        <v>2.217259109894157</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.455993574537221</v>
+        <v>-7.155108477810463</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.2026034026213721</v>
+        <v>0.322957441312075</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.889346341378057</v>
+        <v>-1.603940737695358</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.051749451923174</v>
+        <v>2.222992814132793</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.209006324344268</v>
+        <v>-6.908121227617511</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.291661040304688</v>
+        <v>0.4120150789953909</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.642359091185105</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.19020453964508</v>
+        <v>2.361447901854699</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.945169457140199</v>
+        <v>-6.644284360413442</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3873123058734076</v>
+        <v>0.5076663445641105</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.642359091185105</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.180321058332172</v>
+        <v>2.351564420541792</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.677927656271803</v>
+        <v>-6.377042559545045</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4923744657213929</v>
+        <v>0.6127285044120958</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.642359091185105</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.178486497832798</v>
+        <v>2.349729860042418</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.402118492871319</v>
+        <v>-6.101233396144561</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6023978161081254</v>
+        <v>0.7227518547988283</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.553339782906371</v>
+        <v>-1.267934179223672</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.231597767826578</v>
+        <v>2.402841130036197</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.133050905104339</v>
+        <v>-5.832165808377582</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7106933573604111</v>
+        <v>0.831047396051114</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.284272195139392</v>
+        <v>-0.9988665914566929</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.393706826632259</v>
+        <v>2.564950188841879</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.868990966781543</v>
+        <v>-5.568105870054786</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8030570165277773</v>
+        <v>0.9234110552184802</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.020212256816596</v>
+        <v>-0.7348066531338967</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.538882473464185</v>
+        <v>2.710125835673804</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.161911343276705</v>
+        <v>-4.861026246549947</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.083101832269412</v>
+        <v>1.203455870960115</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.020212256816596</v>
+        <v>-0.7348066531338967</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.536095439803884</v>
+        <v>2.707338802013503</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.912270313290753</v>
+        <v>-4.611385216563995</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.183301868151634</v>
+        <v>1.303655906842337</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.7705712268306439</v>
+        <v>-0.485165623147945</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.686223681683297</v>
+        <v>2.857467043892916</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.657728413949677</v>
+        <v>-4.35684331722292</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.284485449108821</v>
+        <v>1.404839487799524</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.5160293274895684</v>
+        <v>-0.2306237238068695</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.838315642508698</v>
+        <v>3.009559004718318</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.424247191720078</v>
+        <v>-4.123362094993321</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.385802366838513</v>
+        <v>1.506156405529216</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.2825481052599699</v>
+        <v>0.002857498422729088</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.98632880468431</v>
+        <v>3.157572166893929</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.244538661576206</v>
+        <v>-3.943653564849448</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.454793568583103</v>
+        <v>1.575147607273806</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.2253766010972738</v>
+        <v>0.06002900258542521</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.017739496868968</v>
+        <v>3.188982859078588</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.112263187945319</v>
+        <v>-3.811378091218562</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.503071244782485</v>
+        <v>1.623425283473187</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.0931011274663871</v>
+        <v>0.1923044762163119</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.092472267794527</v>
+        <v>3.263715630004147</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.921663513272167</v>
+        <v>-3.620778416545409</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.582126175339382</v>
+        <v>1.702480214030085</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.09749854720676576</v>
+        <v>0.3829041508894647</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.209647133286056</v>
+        <v>3.380890495495675</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.672663714588586</v>
+        <v>-3.371778617861829</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.694632436036473</v>
+        <v>1.814986474727176</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.3464983458903464</v>
+        <v>0.6319039495730454</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.371953353719863</v>
+        <v>3.543196715929482</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.481284639727646</v>
+        <v>-3.180399543000889</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.643208136381631</v>
+        <v>1.763562175072334</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.5378774207512865</v>
+        <v>0.8232830244339855</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.358804869037209</v>
+        <v>3.530048231246828</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.202257344072019</v>
+        <v>-2.901372247345262</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.803363396520968</v>
+        <v>1.923717435211671</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.5378774207512865</v>
+        <v>0.8232830244339855</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.407349210914295</v>
+        <v>3.578592573123914</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.925519169401207</v>
+        <v>-2.624634072674449</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.917437678375287</v>
+        <v>2.03779171706599</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.7196940818612123</v>
+        <v>1.005099685543911</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.519818219566245</v>
+        <v>3.691061581775864</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.798626762966137</v>
+        <v>-2.49774166623938</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.959480654695837</v>
+        <v>2.07983469338654</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.8465864882962822</v>
+        <v>1.131992091978981</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.587239677173809</v>
+        <v>3.758483039383428</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.609091719118912</v>
+        <v>-2.305278816771313</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.028334060139634</v>
+        <v>2.149859221078674</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.036121532143507</v>
+        <v>1.131992091978981</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.69400009138705</v>
+        <v>3.751522427288335</v>
       </c>
     </row>
   </sheetData>
